--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_33.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_33.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IV2</t>
+          <t>Diagnosis</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV2</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9307925129616454</v>
+        <v>-1.439988407751933</v>
       </c>
       <c r="C2">
-        <v>-1.284085373921865</v>
+        <v>0.1127238046819473</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.1043470529185315</v>
+        <v>-1.814285042377336</v>
       </c>
       <c r="C3">
-        <v>-0.6504597206344451</v>
+        <v>0.3626038756010458</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.005143848011511</v>
+        <v>-0.155669801225418</v>
       </c>
       <c r="C4">
-        <v>-1.140998118538927</v>
+        <v>1.317923981404449</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.8351608400271705</v>
+        <v>-0.1632618673206217</v>
       </c>
       <c r="C5">
-        <v>0.5588783284209395</v>
+        <v>-1.174271470339031</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1520176624298365</v>
+        <v>-1.371870156549919</v>
       </c>
       <c r="C6">
-        <v>0.3685164125860022</v>
+        <v>-1.696369536674867</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.2476111851127856</v>
+        <v>0.3877941945329612</v>
       </c>
       <c r="C7">
-        <v>-1.255990189094353</v>
+        <v>1.218813431561053</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.03229660111695248</v>
+        <v>0.8659294697422071</v>
       </c>
       <c r="C8">
-        <v>0.6394978438968502</v>
+        <v>-0.474038476960584</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.09651727234203243</v>
+        <v>-0.6058389013999997</v>
       </c>
       <c r="C9">
-        <v>0.3943931604142192</v>
+        <v>0.236340314391514</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.821940258825561</v>
+        <v>-0.6276389138520408</v>
       </c>
       <c r="C10">
-        <v>-1.260864905926772</v>
+        <v>-1.6329158286609</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>1.075330397725309</v>
+        <v>0.4970271753674914</v>
       </c>
       <c r="C11">
-        <v>-0.874826583978878</v>
+        <v>0.1511846159957131</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.023848458203797</v>
+        <v>-1.148962299955312</v>
       </c>
       <c r="C12">
-        <v>-0.3604626438232494</v>
+        <v>-0.4149512395895452</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.644545901267652</v>
+        <v>-1.505279560261422</v>
       </c>
       <c r="C13">
-        <v>2.31606465603804</v>
+        <v>-0.399631024388851</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.086857331085071</v>
+        <v>0.4689254212424981</v>
       </c>
       <c r="C14">
-        <v>-0.8050207450430296</v>
+        <v>0.8230350491555127</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.7641840551613008</v>
+        <v>0.5613885575956831</v>
       </c>
       <c r="C15">
-        <v>-0.2480749213728174</v>
+        <v>0.1874545209235674</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.002098020871046641</v>
+        <v>-1.550628457812707</v>
       </c>
       <c r="C16">
-        <v>-0.8240975662699096</v>
+        <v>-0.9345036739912527</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.02805462548652497</v>
+        <v>0.9347363104976791</v>
       </c>
       <c r="C17">
-        <v>-0.1219599697197341</v>
+        <v>0.4534909038407481</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.6188179125234424</v>
+        <v>-0.7452980172102164</v>
       </c>
       <c r="C18">
-        <v>-0.2161596360511471</v>
+        <v>-1.601656495556462</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.6485607890624933</v>
+        <v>1.000210479525502</v>
       </c>
       <c r="C19">
-        <v>0.7159676942911692</v>
+        <v>-0.243113058018997</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.618157438868552</v>
+        <v>-0.6002135161144194</v>
       </c>
       <c r="C20">
-        <v>-3.1891657719708</v>
+        <v>-0.8003812216910654</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.497490291240466</v>
+        <v>0.6559311180270178</v>
       </c>
       <c r="C21">
-        <v>0.8273007708413203</v>
+        <v>1.320686926681762</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.7025614033239335</v>
+        <v>0.5226003926838603</v>
       </c>
       <c r="C22">
-        <v>0.7071819041473935</v>
+        <v>1.364252627720983</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.342357907272382</v>
+        <v>0.4180610343693483</v>
       </c>
       <c r="C23">
-        <v>1.947829523405861</v>
+        <v>-0.9602078578877001</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.3714388076019691</v>
+        <v>0.7445237415113732</v>
       </c>
       <c r="C24">
-        <v>0.1412355008809539</v>
+        <v>0.5911151339247243</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.5611060845049658</v>
+        <v>-0.7560992480351421</v>
       </c>
       <c r="C25">
-        <v>0.1332476806337021</v>
+        <v>0.2353831697800834</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.85788905980281</v>
+        <v>-0.8975629166003931</v>
       </c>
       <c r="C26">
-        <v>-0.7442451877625871</v>
+        <v>0.3818730084022433</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-0.3464357549390237</v>
+        <v>-0.6113623206125059</v>
       </c>
       <c r="C27">
-        <v>0.7730774710849496</v>
+        <v>0.799975812751556</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.6184997796490599</v>
+        <v>1.932317220929623</v>
       </c>
       <c r="C28">
-        <v>-0.9964745449819035</v>
+        <v>-0.06046211741326235</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.08876006874068802</v>
+        <v>1.278491431925237</v>
       </c>
       <c r="C29">
-        <v>0.8025499620604667</v>
+        <v>0.3627642511242141</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.06117166834475037</v>
+        <v>-1.835149302296806</v>
       </c>
       <c r="C30">
-        <v>0.2137479531863218</v>
+        <v>-0.3272162968479199</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-1.171282559984486</v>
+        <v>-0.8505140618331535</v>
       </c>
       <c r="C31">
-        <v>0.4292012277816796</v>
+        <v>-1.146315348909512</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.5981796049566513</v>
+        <v>1.491975319700634</v>
       </c>
       <c r="C32">
-        <v>2.762882120078335</v>
+        <v>-1.735089472818119</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.8578968474725766</v>
+        <v>-0.382229039004734</v>
       </c>
       <c r="C33">
-        <v>-0.373082804440163</v>
+        <v>0.2822720918166038</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.9006688222579765</v>
+        <v>-1.130735262886434</v>
       </c>
       <c r="C34">
-        <v>1.726935681446826</v>
+        <v>-0.7169939544691688</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.1965301606524138</v>
+        <v>0.6000106915222361</v>
       </c>
       <c r="C35">
-        <v>-1.286602209526694</v>
+        <v>0.3389239490628221</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.31681156703475</v>
+        <v>-0.4684708435567367</v>
       </c>
       <c r="C36">
-        <v>1.728334205576486</v>
+        <v>-0.5577871526173015</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.0662935154427</v>
+        <v>0.08360422829421837</v>
       </c>
       <c r="C37">
-        <v>-0.4267072230775425</v>
+        <v>0.2487556881405907</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.323912391880377</v>
+        <v>0.5091969833008074</v>
       </c>
       <c r="C38">
-        <v>-2.067969671926548</v>
+        <v>1.208787119326522</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.4891625899725393</v>
+        <v>-0.4941823018946412</v>
       </c>
       <c r="C39">
-        <v>1.318290641515996</v>
+        <v>-2.125539126284798</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.76335845566429</v>
+        <v>0.6429977377660184</v>
       </c>
       <c r="C40">
-        <v>-0.8360580546009891</v>
+        <v>0.479487688356186</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.103944728589286</v>
+        <v>-0.6471664129203164</v>
       </c>
       <c r="C41">
-        <v>-1.020362825520502</v>
+        <v>-0.349947142662909</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.7490269628879728</v>
+        <v>-0.461801979152262</v>
       </c>
       <c r="C42">
-        <v>0.003187124592975932</v>
+        <v>-1.068770513451983</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.8521177099065409</v>
+        <v>-0.04485351797554933</v>
       </c>
       <c r="C43">
-        <v>0.2175306891808163</v>
+        <v>1.15075485032787</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.5015086696242482</v>
+        <v>-1.449076268126932</v>
       </c>
       <c r="C44">
-        <v>0.4635621177873864</v>
+        <v>-0.9609244710563746</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.2119387239823682</v>
+        <v>1.232319472095472</v>
       </c>
       <c r="C45">
-        <v>0.8317788352301139</v>
+        <v>-0.6869609021725532</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.658879639761487</v>
+        <v>-0.715867107700551</v>
       </c>
       <c r="C46">
-        <v>0.5120606138444421</v>
+        <v>-0.583576506309252</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.241146848987681</v>
+        <v>-0.1096153529773694</v>
       </c>
       <c r="C47">
-        <v>-0.02226052227183917</v>
+        <v>0.4898476575967773</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>2.798215359029155</v>
+        <v>-1.116864111397957</v>
       </c>
       <c r="C48">
-        <v>-3.200587762926731</v>
+        <v>-1.802112213800019</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.9019225414189793</v>
+        <v>-0.9960705794221906</v>
       </c>
       <c r="C49">
-        <v>-0.3999014775300248</v>
+        <v>-1.741997618427845</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.0359805832329442</v>
+        <v>1.886369747901369</v>
       </c>
       <c r="C50">
-        <v>-0.5372275874849162</v>
+        <v>-0.05616861034168441</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.2009387109184432</v>
+        <v>-0.3646737936766719</v>
       </c>
       <c r="C51">
-        <v>-0.3263827653331655</v>
+        <v>0.2228268740639792</v>
       </c>
     </row>
   </sheetData>
